--- a/Timesheet.xlsx
+++ b/Timesheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\VSprojects1\PepperCone\CpESeniorDesign-Peppers-Cone\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EDCD81-A3CD-49B7-9FD5-D808B41D58F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0817B8C6-1D7D-412C-A1A6-6259A7D19E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Gabriel" sheetId="1" r:id="rId1"/>
@@ -827,11 +827,13 @@
       <c r="A2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="5">
+        <v>46032</v>
+      </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="13">
-        <f t="shared" ref="E2:E18" si="0">D2-C2</f>
+        <f t="shared" ref="E2:E17" si="0">D2-C2</f>
         <v>0</v>
       </c>
       <c r="F2" s="8"/>
@@ -1072,7 +1074,7 @@
       <c r="C19" s="12"/>
       <c r="D19" s="12"/>
       <c r="E19" s="13">
-        <f t="shared" ref="E2:E256" si="1">D19-C19</f>
+        <f t="shared" ref="E19:E256" si="1">D19-C19</f>
         <v>0</v>
       </c>
       <c r="F19" s="14"/>
@@ -14724,7 +14726,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="13">
-        <f t="shared" ref="E2:E18" si="0">D2-C2</f>
+        <f t="shared" ref="E2:E17" si="0">D2-C2</f>
         <v>0</v>
       </c>
       <c r="F2" s="8"/>
@@ -25675,7 +25677,7 @@
       <c r="C784" s="6"/>
       <c r="D784" s="6"/>
       <c r="E784" s="7">
-        <f t="shared" ref="E784:E958" si="4">D784-C784</f>
+        <f t="shared" ref="E784:E941" si="4">D784-C784</f>
         <v>0</v>
       </c>
       <c r="F784" s="8"/>
@@ -28617,7 +28619,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="13">
-        <f t="shared" ref="E2:E18" si="0">D2-C2</f>
+        <f t="shared" ref="E2:E17" si="0">D2-C2</f>
         <v>0</v>
       </c>
       <c r="F2" s="8"/>
@@ -39568,7 +39570,7 @@
       <c r="C784" s="6"/>
       <c r="D784" s="6"/>
       <c r="E784" s="7">
-        <f t="shared" ref="E784:E958" si="4">D784-C784</f>
+        <f t="shared" ref="E784:E941" si="4">D784-C784</f>
         <v>0</v>
       </c>
       <c r="F784" s="8"/>
@@ -42510,7 +42512,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="13">
-        <f t="shared" ref="E2:E18" si="0">D2-C2</f>
+        <f t="shared" ref="E2:E17" si="0">D2-C2</f>
         <v>0</v>
       </c>
       <c r="F2" s="8"/>
@@ -53461,7 +53463,7 @@
       <c r="C784" s="6"/>
       <c r="D784" s="6"/>
       <c r="E784" s="7">
-        <f t="shared" ref="E784:E958" si="4">D784-C784</f>
+        <f t="shared" ref="E784:E941" si="4">D784-C784</f>
         <v>0</v>
       </c>
       <c r="F784" s="8"/>
@@ -56403,7 +56405,7 @@
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
       <c r="E2" s="13">
-        <f t="shared" ref="E2:E18" si="0">D2-C2</f>
+        <f t="shared" ref="E2:E17" si="0">D2-C2</f>
         <v>0</v>
       </c>
       <c r="F2" s="8"/>
@@ -67354,7 +67356,7 @@
       <c r="C784" s="6"/>
       <c r="D784" s="6"/>
       <c r="E784" s="7">
-        <f t="shared" ref="E784:E958" si="4">D784-C784</f>
+        <f t="shared" ref="E784:E941" si="4">D784-C784</f>
         <v>0</v>
       </c>
       <c r="F784" s="8"/>
